--- a/research/traditional_assets/database/data/slovenia/slovenia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0776</v>
+        <v>0.07919999999999999</v>
       </c>
       <c r="E2">
-        <v>0.285</v>
+        <v>0.151</v>
       </c>
       <c r="F2">
         <v>-0.0202</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>429.5</v>
+        <v>400.7</v>
       </c>
       <c r="L2">
-        <v>0.556996498508624</v>
+        <v>0.5366997053308331</v>
       </c>
       <c r="M2">
-        <v>14.8</v>
+        <v>136.4</v>
       </c>
       <c r="N2">
-        <v>0.008577223993045495</v>
+        <v>0.1022642075273654</v>
       </c>
       <c r="O2">
-        <v>0.03445867287543655</v>
+        <v>0.3404042924881457</v>
       </c>
       <c r="P2">
-        <v>14.8</v>
+        <v>136.4</v>
       </c>
       <c r="Q2">
-        <v>0.008577223993045495</v>
+        <v>0.1022642075273654</v>
       </c>
       <c r="R2">
-        <v>0.03445867287543655</v>
+        <v>0.3404042924881457</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1439</v>
+        <v>935.1</v>
       </c>
       <c r="V2">
-        <v>0.8339611706751666</v>
+        <v>0.7010796221322537</v>
       </c>
       <c r="W2">
-        <v>0.2065598999663348</v>
+        <v>0.161513966705631</v>
       </c>
       <c r="X2">
-        <v>0.06811655357804554</v>
+        <v>0.09500826939216314</v>
       </c>
       <c r="Y2">
-        <v>0.1384433463882893</v>
+        <v>0.06650569731346787</v>
       </c>
       <c r="Z2">
-        <v>0.3706213711693005</v>
+        <v>0.288027900050538</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05226881051860489</v>
+        <v>0.08007328949312822</v>
       </c>
       <c r="AC2">
-        <v>-0.05226881051860489</v>
+        <v>-0.08007328949312822</v>
       </c>
       <c r="AD2">
-        <v>1554.3</v>
+        <v>968.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1554.3</v>
+        <v>968.7</v>
       </c>
       <c r="AG2">
-        <v>115.3</v>
+        <v>33.60000000000002</v>
       </c>
       <c r="AH2">
-        <v>0.4739008476126593</v>
+        <v>0.4207166123778502</v>
       </c>
       <c r="AI2">
-        <v>0.3695259379011935</v>
+        <v>0.2918474331164136</v>
       </c>
       <c r="AJ2">
-        <v>0.06263581051716642</v>
+        <v>0.02457218078104433</v>
       </c>
       <c r="AK2">
-        <v>0.04166666666666665</v>
+        <v>0.01409336856675476</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0776</v>
+        <v>0.07919999999999999</v>
       </c>
       <c r="E3">
-        <v>0.285</v>
+        <v>0.151</v>
       </c>
       <c r="F3">
         <v>-0.0202</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>429.5</v>
+        <v>400.7</v>
       </c>
       <c r="L3">
-        <v>0.556996498508624</v>
+        <v>0.5366997053308331</v>
       </c>
       <c r="M3">
-        <v>14.8</v>
+        <v>136.4</v>
       </c>
       <c r="N3">
-        <v>0.008577223993045495</v>
+        <v>0.1022642075273654</v>
       </c>
       <c r="O3">
-        <v>0.03445867287543655</v>
+        <v>0.3404042924881457</v>
       </c>
       <c r="P3">
-        <v>14.8</v>
+        <v>136.4</v>
       </c>
       <c r="Q3">
-        <v>0.008577223993045495</v>
+        <v>0.1022642075273654</v>
       </c>
       <c r="R3">
-        <v>0.03445867287543655</v>
+        <v>0.3404042924881457</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1439</v>
+        <v>935.1</v>
       </c>
       <c r="V3">
-        <v>0.8339611706751666</v>
+        <v>0.7010796221322537</v>
       </c>
       <c r="W3">
-        <v>0.2065598999663348</v>
+        <v>0.161513966705631</v>
       </c>
       <c r="X3">
-        <v>0.06811655357804554</v>
+        <v>0.09500826939216314</v>
       </c>
       <c r="Y3">
-        <v>0.1384433463882893</v>
+        <v>0.06650569731346787</v>
       </c>
       <c r="Z3">
-        <v>0.3706213711693005</v>
+        <v>0.288027900050538</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05226881051860489</v>
+        <v>0.08007328949312822</v>
       </c>
       <c r="AC3">
-        <v>-0.05226881051860489</v>
+        <v>-0.08007328949312822</v>
       </c>
       <c r="AD3">
-        <v>1554.3</v>
+        <v>968.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1554.3</v>
+        <v>968.7</v>
       </c>
       <c r="AG3">
-        <v>115.3</v>
+        <v>33.60000000000002</v>
       </c>
       <c r="AH3">
-        <v>0.4739008476126593</v>
+        <v>0.4207166123778502</v>
       </c>
       <c r="AI3">
-        <v>0.3695259379011935</v>
+        <v>0.2918474331164136</v>
       </c>
       <c r="AJ3">
-        <v>0.06263581051716642</v>
+        <v>0.02457218078104433</v>
       </c>
       <c r="AK3">
-        <v>0.04166666666666665</v>
+        <v>0.01409336856675476</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/slovenia/slovenia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07919999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="E2">
-        <v>0.151</v>
+        <v>0.18</v>
       </c>
       <c r="F2">
         <v>-0.0202</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>400.7</v>
+        <v>482.7</v>
       </c>
       <c r="L2">
-        <v>0.5366997053308331</v>
+        <v>0.425136515765369</v>
       </c>
       <c r="M2">
-        <v>136.4</v>
+        <v>119.4</v>
       </c>
       <c r="N2">
-        <v>0.1022642075273654</v>
+        <v>0.0635410568889362</v>
       </c>
       <c r="O2">
-        <v>0.3404042924881457</v>
+        <v>0.2473586078309509</v>
       </c>
       <c r="P2">
-        <v>136.4</v>
+        <v>119.4</v>
       </c>
       <c r="Q2">
-        <v>0.1022642075273654</v>
+        <v>0.0635410568889362</v>
       </c>
       <c r="R2">
-        <v>0.3404042924881457</v>
+        <v>0.2473586078309509</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>935.1</v>
+        <v>1276.1</v>
       </c>
       <c r="V2">
-        <v>0.7010796221322537</v>
+        <v>0.6791016976212016</v>
       </c>
       <c r="W2">
-        <v>0.161513966705631</v>
+        <v>0.2103817991631799</v>
       </c>
       <c r="X2">
-        <v>0.09500826939216314</v>
+        <v>0.0821722628208453</v>
       </c>
       <c r="Y2">
-        <v>0.06650569731346787</v>
+        <v>0.1282095363423346</v>
       </c>
       <c r="Z2">
-        <v>0.288027900050538</v>
+        <v>0.4884407237560979</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08007328949312822</v>
+        <v>0.06874534750960676</v>
       </c>
       <c r="AC2">
-        <v>-0.08007328949312822</v>
+        <v>-0.06874534750960676</v>
       </c>
       <c r="AD2">
-        <v>968.7</v>
+        <v>1703.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>968.7</v>
+        <v>1703.4</v>
       </c>
       <c r="AG2">
-        <v>33.60000000000002</v>
+        <v>427.3000000000002</v>
       </c>
       <c r="AH2">
-        <v>0.4207166123778502</v>
+        <v>0.4754780181437544</v>
       </c>
       <c r="AI2">
-        <v>0.2918474331164136</v>
+        <v>0.3652543099751265</v>
       </c>
       <c r="AJ2">
-        <v>0.02457218078104433</v>
+        <v>0.1852670828997573</v>
       </c>
       <c r="AK2">
-        <v>0.01409336856675476</v>
+        <v>0.1261402214022141</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07919999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="E3">
-        <v>0.151</v>
+        <v>0.18</v>
       </c>
       <c r="F3">
         <v>-0.0202</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>400.7</v>
+        <v>482.7</v>
       </c>
       <c r="L3">
-        <v>0.5366997053308331</v>
+        <v>0.425136515765369</v>
       </c>
       <c r="M3">
-        <v>136.4</v>
+        <v>119.4</v>
       </c>
       <c r="N3">
-        <v>0.1022642075273654</v>
+        <v>0.0635410568889362</v>
       </c>
       <c r="O3">
-        <v>0.3404042924881457</v>
+        <v>0.2473586078309509</v>
       </c>
       <c r="P3">
-        <v>136.4</v>
+        <v>119.4</v>
       </c>
       <c r="Q3">
-        <v>0.1022642075273654</v>
+        <v>0.0635410568889362</v>
       </c>
       <c r="R3">
-        <v>0.3404042924881457</v>
+        <v>0.2473586078309509</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>935.1</v>
+        <v>1276.1</v>
       </c>
       <c r="V3">
-        <v>0.7010796221322537</v>
+        <v>0.6791016976212016</v>
       </c>
       <c r="W3">
-        <v>0.161513966705631</v>
+        <v>0.2103817991631799</v>
       </c>
       <c r="X3">
-        <v>0.09500826939216314</v>
+        <v>0.0821722628208453</v>
       </c>
       <c r="Y3">
-        <v>0.06650569731346787</v>
+        <v>0.1282095363423346</v>
       </c>
       <c r="Z3">
-        <v>0.288027900050538</v>
+        <v>0.4884407237560979</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.08007328949312822</v>
+        <v>0.06874534750960676</v>
       </c>
       <c r="AC3">
-        <v>-0.08007328949312822</v>
+        <v>-0.06874534750960676</v>
       </c>
       <c r="AD3">
-        <v>968.7</v>
+        <v>1703.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>968.7</v>
+        <v>1703.4</v>
       </c>
       <c r="AG3">
-        <v>33.60000000000002</v>
+        <v>427.3000000000002</v>
       </c>
       <c r="AH3">
-        <v>0.4207166123778502</v>
+        <v>0.4754780181437544</v>
       </c>
       <c r="AI3">
-        <v>0.2918474331164136</v>
+        <v>0.3652543099751265</v>
       </c>
       <c r="AJ3">
-        <v>0.02457218078104433</v>
+        <v>0.1852670828997573</v>
       </c>
       <c r="AK3">
-        <v>0.01409336856675476</v>
+        <v>0.1261402214022141</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/slovenia/slovenia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.14</v>
+        <v>0.181</v>
       </c>
       <c r="E2">
-        <v>0.18</v>
+        <v>0.233</v>
       </c>
       <c r="F2">
         <v>-0.0202</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>482.7</v>
+        <v>659.5</v>
       </c>
       <c r="L2">
-        <v>0.425136515765369</v>
+        <v>0.4668365541162313</v>
       </c>
       <c r="M2">
-        <v>119.4</v>
+        <v>193.8</v>
       </c>
       <c r="N2">
-        <v>0.0635410568889362</v>
+        <v>0.07340909090909091</v>
       </c>
       <c r="O2">
-        <v>0.2473586078309509</v>
+        <v>0.2938589840788476</v>
       </c>
       <c r="P2">
-        <v>119.4</v>
+        <v>193.8</v>
       </c>
       <c r="Q2">
-        <v>0.0635410568889362</v>
+        <v>0.07340909090909091</v>
       </c>
       <c r="R2">
-        <v>0.2473586078309509</v>
+        <v>0.2938589840788476</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1276.1</v>
+        <v>1243.6</v>
       </c>
       <c r="V2">
-        <v>0.6791016976212016</v>
+        <v>0.471060606060606</v>
       </c>
       <c r="W2">
-        <v>0.2103817991631799</v>
+        <v>0.2278380432529538</v>
       </c>
       <c r="X2">
-        <v>0.0821722628208453</v>
+        <v>0.0841516974567626</v>
       </c>
       <c r="Y2">
-        <v>0.1282095363423346</v>
+        <v>0.1436863457961912</v>
       </c>
       <c r="Z2">
-        <v>0.4884407237560979</v>
+        <v>0.4263519100879443</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06874534750960676</v>
+        <v>0.07189446695737341</v>
       </c>
       <c r="AC2">
-        <v>-0.06874534750960676</v>
+        <v>-0.07189446695737341</v>
       </c>
       <c r="AD2">
-        <v>1703.4</v>
+        <v>2093.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1703.4</v>
+        <v>2093.2</v>
       </c>
       <c r="AG2">
-        <v>427.3000000000002</v>
+        <v>849.5999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.4754780181437544</v>
+        <v>0.442237809515761</v>
       </c>
       <c r="AI2">
-        <v>0.3652543099751265</v>
+        <v>0.3617822945832901</v>
       </c>
       <c r="AJ2">
-        <v>0.1852670828997573</v>
+        <v>0.2434662998624484</v>
       </c>
       <c r="AK2">
-        <v>0.1261402214022141</v>
+        <v>0.1870459248822157</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.14</v>
+        <v>0.181</v>
       </c>
       <c r="E3">
-        <v>0.18</v>
+        <v>0.233</v>
       </c>
       <c r="F3">
         <v>-0.0202</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>482.7</v>
+        <v>659.5</v>
       </c>
       <c r="L3">
-        <v>0.425136515765369</v>
+        <v>0.4668365541162313</v>
       </c>
       <c r="M3">
-        <v>119.4</v>
+        <v>193.8</v>
       </c>
       <c r="N3">
-        <v>0.0635410568889362</v>
+        <v>0.07340909090909091</v>
       </c>
       <c r="O3">
-        <v>0.2473586078309509</v>
+        <v>0.2938589840788476</v>
       </c>
       <c r="P3">
-        <v>119.4</v>
+        <v>193.8</v>
       </c>
       <c r="Q3">
-        <v>0.0635410568889362</v>
+        <v>0.07340909090909091</v>
       </c>
       <c r="R3">
-        <v>0.2473586078309509</v>
+        <v>0.2938589840788476</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1276.1</v>
+        <v>1243.6</v>
       </c>
       <c r="V3">
-        <v>0.6791016976212016</v>
+        <v>0.471060606060606</v>
       </c>
       <c r="W3">
-        <v>0.2103817991631799</v>
+        <v>0.2278380432529538</v>
       </c>
       <c r="X3">
-        <v>0.0821722628208453</v>
+        <v>0.0841516974567626</v>
       </c>
       <c r="Y3">
-        <v>0.1282095363423346</v>
+        <v>0.1436863457961912</v>
       </c>
       <c r="Z3">
-        <v>0.4884407237560979</v>
+        <v>0.4263519100879443</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06874534750960676</v>
+        <v>0.07189446695737341</v>
       </c>
       <c r="AC3">
-        <v>-0.06874534750960676</v>
+        <v>-0.07189446695737341</v>
       </c>
       <c r="AD3">
-        <v>1703.4</v>
+        <v>2093.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1703.4</v>
+        <v>2093.2</v>
       </c>
       <c r="AG3">
-        <v>427.3000000000002</v>
+        <v>849.5999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.4754780181437544</v>
+        <v>0.442237809515761</v>
       </c>
       <c r="AI3">
-        <v>0.3652543099751265</v>
+        <v>0.3617822945832901</v>
       </c>
       <c r="AJ3">
-        <v>0.1852670828997573</v>
+        <v>0.2434662998624484</v>
       </c>
       <c r="AK3">
-        <v>0.1261402214022141</v>
+        <v>0.1870459248822157</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/slovenia/slovenia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_bank_money_center.xlsx
@@ -648,10 +648,10 @@
         <v>0.2278380432529538</v>
       </c>
       <c r="X2">
-        <v>0.0841516974567626</v>
+        <v>0.08413871367287679</v>
       </c>
       <c r="Y2">
-        <v>0.1436863457961912</v>
+        <v>0.143699329580077</v>
       </c>
       <c r="Z2">
         <v>0.4263519100879443</v>
@@ -660,10 +660,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07189446695737341</v>
+        <v>0.07188722509363248</v>
       </c>
       <c r="AC2">
-        <v>-0.07189446695737341</v>
+        <v>-0.07188722509363248</v>
       </c>
       <c r="AD2">
         <v>2093.2</v>
@@ -773,10 +773,10 @@
         <v>0.2278380432529538</v>
       </c>
       <c r="X3">
-        <v>0.0841516974567626</v>
+        <v>0.08413871367287679</v>
       </c>
       <c r="Y3">
-        <v>0.1436863457961912</v>
+        <v>0.143699329580077</v>
       </c>
       <c r="Z3">
         <v>0.4263519100879443</v>
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07189446695737341</v>
+        <v>0.07188722509363248</v>
       </c>
       <c r="AC3">
-        <v>-0.07189446695737341</v>
+        <v>-0.07188722509363248</v>
       </c>
       <c r="AD3">
         <v>2093.2</v>
